--- a/scripts/productos-digitales/guia-chocolateria/build/carta-de-apertura-y-escandallo-chocolate.xlsx
+++ b/scripts/productos-digitales/guia-chocolateria/build/carta-de-apertura-y-escandallo-chocolate.xlsx
@@ -1156,7 +1156,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2 - Direccion, jefes y encargados</t>
+          <t>2 - Dirección, jefes y encargados</t>
         </is>
       </c>
       <c r="D7" s="10" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>Turno manana (07:00-15:00). Tabla salarial de Madrid, marcada EJEMPLO: sustitúyela por la de TU convenio.</t>
+          <t>Turno mañana (07:00-15:00). Tabla salarial de Madrid, marcada EJEMPLO: sustitúyela por la de TU convenio.</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>Base de la fuente: no declarada. Factor 1,5 frente a la de marca, y es la decision de posicionamiento mas cara del negocio (decision 5 del bonus 2). La pagina no declara si el precio lleva IVA: se trata como base imponible y se marca.</t>
+          <t>Base de la fuente: no declarada. Factor 1,5 frente a la de marca, y es la decisión de posicionamiento mas cara del negocio (decisión 5 del bonus 2). La pagina no declara si el precio lleva IVA: se trata como base imponible y se marca.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>Base de la fuente: sin IVA. SUPUESTO declarado. Ojo al chocolate blanco: NO lleva materia seca desgrasada de cacao, y por eso el art. 6.d) del RD 1055/2003 NO le obliga a la mencion «cacao: X % minimo» (`CHN-07`).</t>
+          <t>Base de la fuente: sin IVA. SUPUESTO declarado. Ojo al chocolate blanco: NO lleva materia seca desgrasada de cacao, y por eso el art. 6.d) del RD 1055/2003 NO le obliga a la mención «cacao: X % mínimo» (`CHN-07`).</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>6 dias por semana x 52 semanas = 312, menos 8 dias de cierre por festivos = 304. En agosto la TIENDA NO CIERRA: lo que para es el obrador (D36, y el literal del kit dice «la tienda abre para el turista aunque el obrador pare»). Una bomboneria de menos de 300 m2 tiene libertad horaria por el art. 5.2 de la Ley 1/2004, no por el 5.1 (`CHN-77`).</t>
+          <t>6 días por semana x 52 semanas = 312, menos 8 días de cierre por festivos = 304. En agosto la TIENDA NO CIERRA: lo que para es el obrador (D36, y el literal del kit dice «la tienda abre para el turista aunque el obrador pare»). Una bombonería de menos de 300 m² tiene libertad horaria por el art. 5.2 de la Ley 1/2004, no por el 5.1 (`CHN-77`).</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Almidon de maiz</t>
+          <t>Almidón de maíz</t>
         </is>
       </c>
       <c r="B49" s="23" t="n">
@@ -2799,17 +2799,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Bombon de ganache de chocolate negro 70 %</t>
+          <t>Bombón de ganache de chocolate negro 70 %</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Bombon de chocolate</t>
+          <t>Bombón de chocolate</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="O7" s="13" t="inlineStr">
         <is>
-          <t>La referencia que mas margen deja y la que antes caduca. Con 5,5 g de chocolate sobre 12 g de pieza, el chocolate es el 45,8 % del peso total: cumple el 25 % del ap. 1.13 con holgura. En julio y agosto baja a un tercio de su mix: es la primera que sale del catalogo de verano (literal del kit para junio: «menos ganache fresca»).</t>
+          <t>La referencia que mas margen deja y la que antes caduca. Con 5,5 g de chocolate sobre 12 g de pieza, el chocolate es el 45,8 % del peso total: cumple el 25 % del ap. 1.13 con holgura. En julio y agosto baja a un tercio de su mix: es la primera que sale del catálogo de verano (literal del kit para junio: «menos ganache fresca»).</t>
         </is>
       </c>
     </row>
@@ -2871,17 +2871,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Bombon de ganache de leche y vainilla</t>
+          <t>Bombón de ganache de leche y vainilla</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Bombon de chocolate</t>
+          <t>Bombón de chocolate</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="O8" s="13" t="inlineStr">
         <is>
-          <t>Misma pieza que BC1 con otra formulacion: nata UHT y sorbitol. El kit le da 4-8 semanas frente a los 10-15 dias de BC1. Es LA decision de modelo de negocio del producto, y el libro 5 la cuantifica en euros de merma por caducidad al ano.</t>
+          <t>Misma pieza que BC1 con otra formulación: nata UHT y sorbitol. El kit le da 4-8 semanas frente a los 10-15 días de BC1. Es LA decisión de modelo de negocio del producto, y el libro 5 la cuantifica en euros de merma por caducidad al año.</t>
         </is>
       </c>
     </row>
@@ -2943,17 +2943,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Bombon de praline de avellana</t>
+          <t>Bombón de praline de avellana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Bombon de chocolate (praline)</t>
+          <t>Bombón de chocolate (praline)</t>
         </is>
       </c>
       <c r="E9" s="18" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="O9" s="13" t="inlineStr">
         <is>
-          <t>«Praline» SI significa algo legalmente: es la denominacion de venta europea del bombon de chocolate (`CHN-82`), con el mismo minimo del 25 %. Escribir lo contrario esta prohibido (§5.1, prohibicion 7).</t>
+          <t>«Praline» SI significa algo legalmente: es la denominación de venta europea del bombón de chocolate (`CHN-82`), con el mismo mínimo del 25 %. Escribir lo contrario esta prohibido (§5.1, prohibición 7).</t>
         </is>
       </c>
     </row>
@@ -3015,17 +3015,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Bombon de gianduja de avellana</t>
+          <t>Bombón de gianduja de avellana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Bombon de chocolate</t>
+          <t>Bombón de chocolate</t>
         </is>
       </c>
       <c r="E10" s="18" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="O10" s="13" t="inlineStr">
         <is>
-          <t>La gianduja tiene apartado propio en la norma (1.6.b.3), pero aqui va DENTRO de un bombon: la denominacion de venta que manda es la del producto que vendes, no la del relleno.</t>
+          <t>La gianduja tiene apartado propio en la norma (1.6.b.3), pero aquí va DENTRO de un bombón: la denominación de venta que manda es la del producto que vendes, no la del relleno.</t>
         </is>
       </c>
     </row>
@@ -3092,12 +3092,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Bombon de chocolate</t>
+          <t>Bombón de chocolate</t>
         </is>
       </c>
       <c r="E11" s="18" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="O11" s="13" t="inlineStr">
         <is>
-          <t>Aqui el 25 % se pelea: 4 g de chocolate sobre 13 g de pieza son el 30,8 %, y bajando el bano un gramo se cae por debajo del minimo legal. Es el ejemplo con el que el semaforo del libro 4 ensena para que sirve. «Trufa» no es una categoria legal espanola (`CHN-03b`).</t>
+          <t>Aquí el 25 % se pelea: 4 g de chocolate sobre 13 g de pieza son el 30,8 %, y bajando el baño un gramo se cae por debajo del mínimo legal. Es el ejemplo con el que el semáforo del libro 4 enseña para que sirve. «Trufa» no es una categoría legal española (`CHN-03b`).</t>
         </is>
       </c>
     </row>
@@ -3159,17 +3159,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Bombon de licor de ron</t>
+          <t>Bombón de licor de ron</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Bombon de chocolate</t>
+          <t>Bombón de chocolate</t>
         </is>
       </c>
       <c r="E12" s="18" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="O12" s="13" t="inlineStr">
         <is>
-          <t>Cascara mas gruesa (6 g) porque el licor la ataca. La unica del surtido sin leche: si la vendes a granel al lado de las demas, la contaminacion cruzada en la pinza se come esa ventaja.</t>
+          <t>Cascara mas gruesa (6 g) porque el licor la ataca. La única del surtido sin leche: si la vendes a granel al lado de las demás, la contaminación cruzada en la pinza se come esa ventaja.</t>
         </is>
       </c>
     </row>
@@ -3231,17 +3231,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Bombon de caramelo salado</t>
+          <t>Bombón de caramelo salado</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Bombon de chocolate</t>
+          <t>Bombón de chocolate</t>
         </is>
       </c>
       <c r="E13" s="18" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="O13" s="13" t="inlineStr">
         <is>
-          <t>Azucar alto y agua baja: aguanta mucho mas que una ganache fresca.</t>
+          <t>Azúcar alto y agua baja: aguanta mucho mas que una ganache fresca.</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Bombon de praline de cacahuete</t>
+          <t>Bombón de praline de cacahuete</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Bombon de chocolate (praline)</t>
+          <t>Bombón de chocolate (praline)</t>
         </is>
       </c>
       <c r="E14" s="18" t="inlineStr">
@@ -3375,17 +3375,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Bombon crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sesamo y barquillo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Bombon de chocolate</t>
+          <t>Bombón de chocolate</t>
         </is>
       </c>
       <c r="E15" s="18" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="O15" s="13" t="inlineStr">
         <is>
-          <t>Dos alergenos mas que sus companeras, y los dos independientes: granos de sesamo (punto 11) y cereales con gluten del barquillo (punto 1). El kit le da 3-4 semanas, y no por seguridad: pierde el crujiente mucho antes.</t>
+          <t>Dos alérgenos mas que sus companeras, y los dos independientes: granos de sesamo (punto 11) y cereales con gluten del barquillo (punto 1). El kit le da 3-4 semanas, y no por seguridad: pierde el crujiente mucho antes.</t>
         </is>
       </c>
     </row>
@@ -3447,17 +3447,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Bombon de naranja confitada y chocolate negro</t>
+          <t>Bombón de naranja confitada y chocolate negro</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Bombon de chocolate</t>
+          <t>Bombón de chocolate</t>
         </is>
       </c>
       <c r="E16" s="18" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="O16" s="13" t="inlineStr">
         <is>
-          <t>La unica del surtido con SULFITOS, que es el octavo alergeno y el que mas se olvida: la fruta confitada suele llevarlos y el umbral de declaracion es de 10 mg/kg. La fruta ademas contamina el recorte: su merma NO recuperable es la mas alta de la carta (D40).</t>
+          <t>La única del surtido con SULFITOS, que es el octavo alérgeno y el que mas se olvida: la fruta confitada suele llevarlos y el umbral de declaración es de 10 mg/kg. La fruta además contamina el recorte: su merma NO recuperable es la mas alta de la carta (D40).</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="F17" s="29" t="inlineStr">
         <is>
-          <t>ap. 1.6: minimos calculados DESCONTANDO los ingredientes anadidos del ap. 3</t>
+          <t>ap. 1.6: mínimos calculados DESCONTANDO los ingredientes añadidos del ap. 3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="O17" s="13" t="inlineStr">
         <is>
-          <t>La referencia que vende el posicionamiento: cobertura de origen a 37,48 euros/kg (`CHS-28c`) frente a los 25,02 de la de marca (`CHS-28a`), factor 1,5. Lleva la mencion «cacao: X % minimo» obligatoria (`CHN-07`) y es la que mas sube en verano: no lleva agua, aguanta 12-18 meses y viaja. Y es la referencia con el food cost MAS ALTO de la carta, con diferencia: comprar cobertura de origen y ponerle precio de cobertura de marca es como se regala el trabajo. El libro 3 lo ensena con el escenario de subida del cacao.</t>
+          <t>La referencia que vende el posicionamiento: cobertura de origen a 37,48 euros/kg (`CHS-28c`) frente a los 25,02 de la de marca (`CHS-28a`), factor 1,5. Lleva la mención «cacao: X % mínimo» obligatoria (`CHN-07`) y es la que mas sube en verano: no lleva agua, aguanta 12-18 meses y viaja. Y es la referencia con el food cost MAS ALTO de la carta, con diferencia: comprar cobertura de origen y ponerle precio de cobertura de marca es como se regala el trabajo. El libro 3 lo enseña con el escenario de subida del cacao.</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="F18" s="29" t="inlineStr">
         <is>
-          <t>ap. 1.7: minimos calculados DESCONTANDO los ingredientes anadidos del ap. 3</t>
+          <t>ap. 1.7: mínimos calculados DESCONTANDO los ingredientes añadidos del ap. 3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="O18" s="13" t="inlineStr">
         <is>
-          <t>Tambien lleva la mencion «cacao: X % minimo» (`CHN-07`).</t>
+          <t>También lleva la mención «cacao: X % mínimo» (`CHN-07`).</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="O19" s="13" t="inlineStr">
         <is>
-          <t>El chocolate blanco NO lleva la mencion «cacao: X % minimo»: `CHN-07` acota esa obligacion a los apartados 1.4, 1.5, 1.6, 1.7, 1.8, 1.11 y 1.12, y el blanco es el 1.9. Escribir que la mencion es obligatoria en todos los chocolates esta prohibido (§5.1, 27).</t>
+          <t>El chocolate blanco NO lleva la mención «cacao: X % mínimo»: `CHN-07` acota esa obligación a los apartados 1.4, 1.5, 1.6, 1.7, 1.8, 1.11 y 1.12, y el blanco es el 1.9. Escribir que la mención es obligatoria en todos los chocolates esta prohibido (§5.1, 27).</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="F20" s="29" t="inlineStr">
         <is>
-          <t>ap. 1.6 con materias comestibles anadidas del ap. 3: no pueden exceder el 40 % del peso total del producto acabado</t>
+          <t>ap. 1.6 con materias comestibles añadidas del ap. 3: no pueden exceder el 40 % del peso total del producto acabado</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="O20" s="13" t="inlineStr">
         <is>
-          <t>La almendra va en `g_relleno` porque es materia comestible ANADIDA del ap. 3, y su tope es el 40 % del peso total (`CHN-09`). Con 22 g sobre 100 esta en el 22 %: dentro. La almendra enrancia, y el frio no lo evita: manda la fecha, no el aspecto (nota del kit).</t>
+          <t>La almendra va en `g_relleno` porque es materia comestible AÑADIDA del ap. 3, y su tope es el 40 % del peso total (`CHN-09`). Con 22 g sobre 100 esta en el 22 %: dentro. La almendra enrancia, y el frío no lo evita: manda la fecha, no el aspecto (nota del kit).</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="F21" s="29" t="inlineStr">
         <is>
-          <t>ap. 1.7 con materias comestibles anadidas del ap. 3 (tope 40 %)</t>
+          <t>ap. 1.7 con materias comestibles añadidas del ap. 3 (tope 40 %)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="O21" s="13" t="inlineStr">
         <is>
-          <t>La avellana va como materia anadida del ap. 3, igual que la almendra de TB4.</t>
+          <t>La avellana va como materia añadida del ap. 3, igual que la almendra de TB4.</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="O22" s="13" t="inlineStr">
         <is>
-          <t>La segunda referencia del ap. 1.10, y la que ensena la base de calculo: 55 g de chocolate sobre 100 g de pieza son el 55 %, calculado SOBRE EL PESO TOTAL con el relleno dentro (`CHN-10`). Si alguien lo calculase descontando el relleno le saldria el 100 % y el semaforo dejaria pasar cualquier cosa: por eso invertir las dos bases esta prohibido. Y NO es chocolate relleno lo que lleva interior de panaderia, pasteleria, galleteria, bolleria o helado (`CHN-04`).</t>
+          <t>La segunda referencia del ap. 1.10, y la que enseña la base de calculo: 55 g de chocolate sobre 100 g de pieza son el 55 %, calculado SOBRE EL PESO TOTAL con el relleno dentro (`CHN-10`). Si alguien lo calculase descontando el relleno le saldria el 100 % y el semáforo dejaría pasar cualquier cosa: por eso invertir las dos bases esta prohibido. Y NO es chocolate relleno lo que lleva interior de panadería, pastelería, galleteria, bollería o helado (`CHN-04`).</t>
         </is>
       </c>
     </row>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="F23" s="29" t="inlineStr">
         <is>
-          <t>ap. 1.11: 35 % de materia seca total de cacao, 18 % de manteca, 14 % de desgrasada y hasta 8 % de harina o almidon de trigo, arroz o maiz</t>
+          <t>ap. 1.11: 35 % de materia seca total de cacao, 18 % de manteca, 14 % de desgrasada y hasta 8 % de harina o almidón de trigo, arroz o maíz</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="O23" s="13" t="inlineStr">
         <is>
-          <t>El almidon (9,6 g sobre 200, el 4,8 %) esta por debajo del tope del 8 %. Se usa ALMIDON DE MAIZ a proposito: con almidon de TRIGO habria que declarar gluten, y la norma admite los tres. La etiqueta lleva ademas la expresion «para su consumo cocido» (ap. 6.e): es una ADICION ESPANOLA que NO existe en la Directiva 2000/36/CE (`CHN-83`), asi que no se escribe que sea un requisito europeo.</t>
+          <t>El almidón (9,6 g sobre 200, el 4,8 %) esta por debajo del tope del 8 %. Se usa ALMIDÓN DE MAÍZ a propósito: con almidón de TRIGO habría que declarar gluten, y la norma admite los tres. La etiqueta lleva además la expresión «para su consumo cocido» (ap. 6.e): es una ADICION ESPAÑOLA que NO existe en la Directiva 2000/36/CE (`CHN-83`), así que no se escribe que sea un requisito europeo.</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="F24" s="29" t="inlineStr">
         <is>
-          <t>ap. 1.11: 35 % cacao total, 18 % manteca, 14 % desgrasada, almidon hasta 8 %</t>
+          <t>ap. 1.11: 35 % cacao total, 18 % manteca, 14 % desgrasada, almidón hasta 8 %</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="O24" s="13" t="inlineStr">
         <is>
-          <t>Seis sobres de 30 g. Ojo al art. 2.2.c) del RD 1808/1991: los envases cuya cara mayor mide menos de 10 cm2 estan exentos de lote, pero la CAJA que los contiene no (`CHN-36`).</t>
+          <t>Seis sobres de 30 g. Ojo al art. 2.2.c) del RD 1808/1991: los envases cuya cara mayor mide menos de 10 cm2 están exentos de lote, pero la CAJA que los contiene no (`CHN-36`).</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="O25" s="13" t="inlineStr">
         <is>
-          <t>Aqui NO entregas un bien: prestas un servicio de hosteleria, y el IVA va al 10 % por el art. 91.Uno.2.2.o (`CHN-71c`). No lleva etiqueta, asi que su referencia es tu sistema de autocontrol (D47). Y si pones mesas, el art. 8 de la Ley 1/2025 te obliga a facilitar que el cliente se lleve lo que no ha consumido, aunque seas microempresa: la exclusion del art. 6.6 NO alcanza al art. 8 (`CHN-92`). Es la pieza que sube el ticket del churro un 40-60 % en la variante de taza (`CHS-32`), y es OTRO negocio (D1).</t>
+          <t>Aquí NO entregas un bien: prestas un servicio de hostelería, y el IVA va al 10 % por el art. 91.Uno.2.2.o (`CHN-71c`). No lleva etiqueta, así que su referencia es tu sistema de autocontrol (D47). Y si pones mesas, el art. 8 de la Ley 1/2025 te obliga a facilitar que el cliente se lleve lo que no ha consumido, aunque seas microempresa: la exclusión del art. 6.6 NO alcanza al art. 8 (`CHN-92`). Es la pieza que sube el ticket del churro un 40-60 % en la variante de taza (`CHS-32`), y es OTRO negocio (D1).</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="F26" s="29" t="inlineStr">
         <is>
-          <t>ap. 1.7: minimos descontando los ingredientes anadidos del ap. 3</t>
+          <t>ap. 1.7: mínimos descontando los ingredientes añadidos del ap. 3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O26" s="13" t="inlineStr">
         <is>
-          <t>La merma recuperable mas alta del catalogo: la pieza hueca se raja con los cambios bruscos de temperatura (nota del kit) y lo que se rompe SIN relleno vuelve entero a la cuba. Cero mix en verano: es de campana.</t>
+          <t>La merma recuperable mas alta del catálogo: la pieza hueca se raja con los cambios bruscos de temperatura (nota del kit) y lo que se rompe SIN relleno vuelve entero a la cuba. Cero mix en verano: es de campana.</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="F27" s="29" t="inlineStr">
         <is>
-          <t>ap. 1.7 con materias comestibles anadidas del ap. 3 (tope 40 %)</t>
+          <t>ap. 1.7 con materias comestibles añadidas del ap. 3 (tope 40 %)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="O27" s="13" t="inlineStr">
         <is>
-          <t>Pieza de autor y la que mas minutos de obrador se lleva: 210 por tanda de seis. La decoracion va como materia anadida del ap. 3. Es la referencia que pone a prueba la capacidad del libro 1 en abril.</t>
+          <t>Pieza de autor y la que mas minutos de obrador se lleva: 210 por tanda de seis. La decoración va como materia añadida del ap. 3. Es la referencia que pone a prueba la capacidad del libro 1 en abril.</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Producto de confiteria recubierto de chocolate</t>
+          <t>Producto de confitería recubierto de chocolate</t>
         </is>
       </c>
       <c r="E28" s="18" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="F28" s="29" t="inlineStr">
         <is>
-          <t>RD 348/2011: si el producto esta relleno, recubierto o grageado, la denominacion de venta tiene que decirlo</t>
+          <t>RD 348/2011: si el producto esta relleno, recubierto o grageado, la denominación de venta tiene que decirlo</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="O28" s="13" t="inlineStr">
         <is>
-          <t>LA REFERENCIA QUE ROMPE LA REGLA, y por eso esta aqui: 9 g de chocolate sobre 30 g de pieza son el 30 %, pero NO es un bombon de chocolate, porque el 1.13 pide una pieza «del tamano de un bocado constituida por chocolate», y esto es un producto de confiteria RECUBIERTO. Su denominacion sale del RD 348/2011 (`CHN-15`), no del RD 1055/2003. La UNICA con huevo, por la yema, y va con ovoproducto pasteurizado (`CHN-31`). Esta literalmente en el calendario del kit: «Todos los Santos (1): panellets y huesos de santo banados».</t>
+          <t>LA REFERENCIA QUE ROMPE LA REGLA, y por eso esta aquí: 9 g de chocolate sobre 30 g de pieza son el 30 %, pero NO es un bombón de chocolate, porque el 1.13 pide una pieza «del tamaño de un bocado constituida por chocolate», y esto es un producto de confitería RECUBIERTO. Su denominación sale del RD 348/2011 (`CHN-15`), no del RD 1055/2003. La ÚNICA con huevo, por la yema, y va con ovoproducto pasteurizado (`CHN-31`). Esta literalmente en el calendario del kit: «Todos los Santos (1): panellets y huesos de santo banados».</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Turron de chocolate con almendra, 250 g</t>
+          <t>Turrón de chocolate con almendra, 250 g</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="F29" s="29" t="inlineStr">
         <is>
-          <t>ap. 1.6 con materias comestibles anadidas del ap. 3 (tope 40 %)</t>
+          <t>ap. 1.6 con materias comestibles añadidas del ap. 3 (tope 40 %)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="O29" s="13" t="inlineStr">
         <is>
-          <t>HUECO DECLARADO: la denominacion que publica este juego de datos es la del RD 1055/2003, porque la norma de calidad de TURRONES no se abrio en la verificacion legal del 12-09-2026 y ninguna ficha `CHN-*` la cubre. «Turron de chocolate con almendra» es el NOMBRE COMERCIAL; antes de imprimir la etiqueta hay que comprobar si la norma de turrones te obliga a otra denominacion de venta. La almendra (82 g sobre 250, el 32,8 %) esta dentro del tope del 40 % del ap. 3 (`CHN-09`).</t>
+          <t>HUECO DECLARADO: la denominación que publica este juego de datos es la del RD 1055/2003, porque la norma de calidad de TURRONES no se abrio en la verificación legal del 12-09-2026 y ninguna ficha `CHN-*` la cubre. «Turrón de chocolate con almendra» es el NOMBRE COMERCIAL; antes de imprimir la etiqueta hay que comprobar si la norma de turrones te obliga a otra denominación de venta. La almendra (82 g sobre 250, el 32,8 %) esta dentro del tope del 40 % del ap. 3 (`CHN-09`).</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="F30" s="29" t="inlineStr">
         <is>
-          <t>RD 348/2011, ap. 1.3: la denominacion de venta se complementa con «relleno», «recubierto» o «grageado» segun el caso</t>
+          <t>RD 348/2011, ap. 1.3: la denominación de venta se complementa con «relleno», «recubierto» o «grageado» según el caso</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="O30" s="13" t="inlineStr">
         <is>
-          <t>La que da nombre a la casa, y su denominacion NO sale del RD 1055/2003 sino del RD 348/2011: «grageas o confites de chocolate» (`CHN-15`). Se hace en bombo, no en molde: `moldes_tanda` vale 1 y los 95 minutos son de la tanda entera, de la que salen 40 bolsas. Es la segunda que mas sube en verano: no lleva agua y es souvenir (literal del kit para julio: «packs souvenir y colaboraciones locales»).</t>
+          <t>La que da nombre a la casa, y su denominación NO sale del RD 1055/2003 sino del RD 348/2011: «grageas o confites de chocolate» (`CHN-15`). Se hace en bombo, no en molde: `moldes_tanda` vale 1 y los 95 minutos son de la tanda entera, de la que salen 40 bolsas. Es la segunda que mas sube en verano: no lleva agua y es souvenir (literal del kit para julio: «packs souvenir y colaboraciones locales»).</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="F31" s="29" t="inlineStr">
         <is>
-          <t>ap. 6.a) y 6.c): la denominacion va por pieza o, si el surtido es de los aps. 1.6 a 1.10 y 1.13, se sustituye por la de surtido, con una unica lista de ingredientes. Es una DECISION de etiquetado, no una obligacion</t>
+          <t>ap. 6.a) y 6.c): la denominación va por pieza o, si el surtido es de los aps. 1.6 a 1.10 y 1.13, se sustituye por la de surtido, con una única lista de ingredientes. Es una DECISION de etiquetado, no una obligación</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="O31" s="13" t="inlineStr">
         <is>
-          <t>PVP de `CHS-29`, precio de MOSTRADOR (con IVA) y base de IVA NO declarada por la fuente: entra con su columna «lleva IVA» y el libro 4 publica el PVP base por formula, porque el libro 7 pide el ticket medio SIN IVA. 12 unidades a 20,00 euros son 1,67 euros por bombon. Su coste de materia NO se teclea: se COMPONE de las referencias que lleva dentro (`composicion_caja`), y por eso `g_chocolate` vale 0. Los siete alergenos son la UNION de lo que va dentro: en un surtido a granel no puedes prometer que una pinza no ha tocado otra cosa.</t>
+          <t>PVP de `CHS-29`, precio de MOSTRADOR (con IVA) y base de IVA NO declarada por la fuente: entra con su columna «lleva IVA» y el libro 4 publica el PVP base por fórmula, porque el libro 7 pide el ticket medio SIN IVA. 12 unidades a 20,00 euros son 1,67 euros por bombón. Su coste de materia NO se teclea: se COMPONE de las referencias que lleva dentro (`composicion_caja`), y por eso `g_chocolate` vale 0. Los siete alérgenos son la UNIÓN de lo que va dentro: en un surtido a granel no puedes prometer que una pinza no ha tocado otra cosa.</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="O32" s="13" t="inlineStr">
         <is>
-          <t>1,40 euros por bombon: un 16 % menos que en la caja de 12.</t>
+          <t>1,40 euros por bombón: un 16 % menos que en la caja de 12.</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="O33" s="13" t="inlineStr">
         <is>
-          <t>1,29 euros por bombon: un 23 % menos que en la caja de 12. Esa escalera es la decision 4 del bonus 2, y el libro 4 la resuelve comparando el precio de la caja con la suma de sus unidades sueltas.</t>
+          <t>1,29 euros por bombón: un 23 % menos que en la caja de 12. Esa escalera es la decisión 4 del bonus 2, y el libro 4 la resuelve comparando el precio de la caja con la suma de sus unidades sueltas.</t>
         </is>
       </c>
     </row>
@@ -4803,14 +4803,14 @@
       </c>
       <c r="O34" s="13" t="inlineStr">
         <is>
-          <t>SUPUESTO: `CHS-29` no cubre el estuche corporativo. Lo que SI esta verificado es su regla operativa: 14 dias de plazo minimo desde la aprobacion de la muestra (`CHS-55`), que es lo que decide si aceptas un pedido de empresa en diciembre. Y es el canal que te saca de la nota del epigrafe 644.5 y te mete en la tabla de CLIENTES del art. 5.3.b) del EUDR (`CHN-24`, D48).</t>
+          <t>SUPUESTO: `CHS-29` no cubre el estuche corporativo. Lo que SI esta verificado es su regla operativa: 14 días de plazo mínimo desde la aprobación de la muestra (`CHS-55`), que es lo que decide si aceptas un pedido de empresa en diciembre. Y es el canal que te saca de la nota del epígrafe 644.5 y te mete en la tabla de CLIENTES del art. 5.3.b) del EUDR (`CHN-24`, D48).</t>
         </is>
       </c>
     </row>
     <row r="35" ht="46" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>ENVASADO CON ETIQUETA: Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservacion POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran ademas las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</t>
+          <t>ENVASADO CON ETIQUETA: Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>Factor 1,5 frente a la de marca, y es la decision de posicionamiento mas cara del negocio (decision 5 del bonus 2). La pagina no declara si el precio lleva IVA: se trata como base imponible y se marca.</t>
+          <t>Factor 1,5 frente a la de marca, y es la decisión de posicionamiento mas cara del negocio (decisión 5 del bonus 2). La pagina no declara si el precio lleva IVA: se trata como base imponible y se marca.</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>SUPUESTO declarado. Ojo al chocolate blanco: NO lleva materia seca desgrasada de cacao, y por eso el art. 6.d) del RD 1055/2003 NO le obliga a la mencion «cacao: X % minimo» (`CHN-07`).</t>
+          <t>SUPUESTO declarado. Ojo al chocolate blanco: NO lleva materia seca desgrasada de cacao, y por eso el art. 6.d) del RD 1055/2003 NO le obliga a la mención «cacao: X % mínimo» (`CHN-07`).</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Turron de chocolate con almendra, 250 g</t>
+          <t>Turrón de chocolate con almendra, 250 g</t>
         </is>
       </c>
       <c r="C59" s="24">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Almidon de maiz</t>
+          <t>Almidón de maíz</t>
         </is>
       </c>
       <c r="C45" s="31" t="n">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Almidon de maiz</t>
+          <t>Almidón de maíz</t>
         </is>
       </c>
       <c r="C48" s="31" t="n">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10-15 dias</t>
+          <t>10-15 días</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>La ganache que obliga a decidir el modelo de negocio: agua disponible alta, y el kit le da 10-15 dias. Es la que manda en la decision 3 del bonus 2.</t>
+          <t>La ganache que obliga a decidir el modelo de negocio: agua disponible alta, y el kit le da 10-15 días. Es la que manda en la decisión 3 del bonus 2.</t>
         </is>
       </c>
     </row>
@@ -6545,7 +6545,7 @@
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>La misma pieza con otra formulacion: el kit le da 4-8 semanas. Entre esta y la anterior hay un factor DE TRES A CINCO, y esa es una decision de modelo de negocio, no tecnica.</t>
+          <t>La misma pieza con otra formulación: el kit le da 4-8 semanas. Entre esta y la anterior hay un factor DE TRES A CINCO, y esa es una decisión de modelo de negocio, no técnica.</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>«Praline» NO es un nombre comercial: el punto 10 de la parte A del Anexo I de la Directiva 2000/36/CE se titula «Bombon de chocolate o praline» (`CHN-82`), con el mismo minimo del 25 %.</t>
+          <t>«Praline» NO es un nombre comercial: el punto 10 de la parte A del Anexo I de la Directiva 2000/36/CE se titula «Bombón de chocolate o praline» (`CHN-82`), con el mismo mínimo del 25 %.</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>La gianduja tiene su propio apartado en la norma (1.6.b.3), con avellanas entre 20 y 40 g por 100 g. Aqui es RELLENO de un bombon, asi que la denominacion de venta es la del bombon.</t>
+          <t>La gianduja tiene su propio apartado en la norma (1.6.b.3), con avellanas entre 20 y 40 g por 100 g. Aquí es RELLENO de un bombón, así que la denominación de venta es la del bombón.</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>«Trufa» no aparece ni una vez en el RD 1055/2003 (`CHN-03b`): es un TIPO de bombon, no una categoria legal ni un sinonimo de bombon.</t>
+          <t>«Trufa» no aparece ni una vez en el RD 1055/2003 (`CHN-03b`): es un TIPO de bombón, no una categoría legal ni un sinonimo de bombón.</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>El alcohol baja la actividad de agua. Vigilar la cristalizacion del azucar en la cascara: revienta y gotea (nota literal del kit).</t>
+          <t>El alcohol baja la actividad de agua. Vigilar la cristalización del azúcar en la cascara: revienta y gotea (nota literal del kit).</t>
         </is>
       </c>
     </row>
@@ -6675,7 +6675,7 @@
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>Azucar alto y agua baja: aguanta mas que una ganache fresca.</t>
+          <t>Azúcar alto y agua baja: aguanta mas que una ganache fresca.</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>EL CACAHUETE ES EL PUNTO 5 DEL ANEXO II y NO es un fruto de cascara (`CHN-34b`): esta referencia se etiqueta con su propio alergeno, no dentro de «frutos secos».</t>
+          <t>EL CACAHUETE ES EL PUNTO 5 DEL ANEXO II y NO es un fruto de cascara (`CHN-34b`): esta referencia se etiqueta con su propio alérgeno, no dentro de «frutos secos».</t>
         </is>
       </c>
     </row>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>DOS alergenos independientes en una sola pieza: granos de sesamo (punto 11) y cereales con gluten del barquillo (punto 1). El kit le da 3-4 semanas, y no por seguridad: pierde el crujiente mucho antes.</t>
+          <t>DOS alérgenos independientes en una sola pieza: granos de sesamo (punto 11) y cereales con gluten del barquillo (punto 1). El kit le da 3-4 semanas, y no por seguridad: pierde el crujiente mucho antes.</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>La fruta confitada suele llevar SULFITOS (punto 12 del Anexo II), que es el octavo alergeno y el que mas se olvida. Pidele a tu proveedor la ficha tecnica: el umbral de declaracion es 10 mg/kg.</t>
+          <t>La fruta confitada suele llevar SULFITOS (punto 12 del Anexo II), que es el octavo alérgeno y el que mas se olvida. Pidele a tu proveedor la ficha técnica: el umbral de declaración es 10 mg/kg.</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>En una TABLETA RELLENA la denominacion es «chocolate relleno» (ap. 1.10) y el exterior tiene que ser al menos el 25 % del peso total (`CHN-04`), calculado SOBRE EL PESO TOTAL con el relleno dentro (`CHN-10`).</t>
+          <t>En una TABLETA RELLENA la denominación es «chocolate relleno» (ap. 1.10) y el exterior tiene que ser al menos el 25 % del peso total (`CHN-04`), calculado SOBRE EL PESO TOTAL con el relleno dentro (`CHN-10`).</t>
         </is>
       </c>
     </row>
@@ -6805,7 +6805,7 @@
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>NO es un relleno: es la otra mitad de la formula del chocolate a la taza, que NO se hace solo con cobertura. Va aqui para que el escandallo pueda costearla. El almidon es DE MAIZ a proposito: la norma admite trigo, arroz o maiz hasta el 8 %, y con el de trigo habria que declarar gluten.</t>
+          <t>NO es un relleno: es la otra mitad de la fórmula del chocolate a la taza, que NO se hace solo con cobertura. Va aquí para que el escandallo pueda costearla. El almidón es DE MAÍZ a propósito: la norma admite trigo, arroz o maíz hasta el 8 %, y con el de trigo habría que declarar gluten.</t>
         </is>
       </c>
     </row>
@@ -6826,12 +6826,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10-15 dias</t>
+          <t>10-15 días</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>La UNICA referencia del surtido con huevo, y va con ovoproducto pasteurizado de establecimiento autorizado, que es la tercera via del art. 9 del RD 1021/2022 (`CHN-31`). Con huevo crudo habria que llegar a 70 grados C durante 2 s en el centro.</t>
+          <t>La ÚNICA referencia del surtido con huevo, y va con ovoproducto pasteurizado de establecimiento autorizado, que es la tercera vía del art. 9 del RD 1021/2022 (`CHN-31`). Con huevo crudo habría que llegar a 70 °C durante 2 s en el centro.</t>
         </is>
       </c>
     </row>
@@ -6985,12 +6985,12 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Bombon de ganache de chocolate negro 70 %</t>
+          <t>Bombón de ganache de chocolate negro 70 %</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="P70" s="13" t="inlineStr">
         <is>
-          <t>La referencia que mas margen deja y la que antes caduca. Con 5,5 g de chocolate sobre 12 g de pieza, el chocolate es el 45,8 % del peso total: cumple el 25 % del ap. 1.13 con holgura. En julio y agosto baja a un tercio de su mix: es la primera que sale del catalogo de verano (literal del kit para junio: «menos ganache fresca»).</t>
+          <t>La referencia que mas margen deja y la que antes caduca. Con 5,5 g de chocolate sobre 12 g de pieza, el chocolate es el 45,8 % del peso total: cumple el 25 % del ap. 1.13 con holgura. En julio y agosto baja a un tercio de su mix: es la primera que sale del catálogo de verano (literal del kit para junio: «menos ganache fresca»).</t>
         </is>
       </c>
     </row>
@@ -7055,12 +7055,12 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Bombon de ganache de leche y vainilla</t>
+          <t>Bombón de ganache de leche y vainilla</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="P71" s="13" t="inlineStr">
         <is>
-          <t>Misma pieza que BC1 con otra formulacion: nata UHT y sorbitol. El kit le da 4-8 semanas frente a los 10-15 dias de BC1. Es LA decision de modelo de negocio del producto, y el libro 5 la cuantifica en euros de merma por caducidad al ano.</t>
+          <t>Misma pieza que BC1 con otra formulación: nata UHT y sorbitol. El kit le da 4-8 semanas frente a los 10-15 días de BC1. Es LA decisión de modelo de negocio del producto, y el libro 5 la cuantifica en euros de merma por caducidad al año.</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Bombon de praline de avellana</t>
+          <t>Bombón de praline de avellana</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="P72" s="13" t="inlineStr">
         <is>
-          <t>«Praline» SI significa algo legalmente: es la denominacion de venta europea del bombon de chocolate (`CHN-82`), con el mismo minimo del 25 %. Escribir lo contrario esta prohibido (§5.1, prohibicion 7).</t>
+          <t>«Praline» SI significa algo legalmente: es la denominación de venta europea del bombón de chocolate (`CHN-82`), con el mismo mínimo del 25 %. Escribir lo contrario esta prohibido (§5.1, prohibición 7).</t>
         </is>
       </c>
     </row>
@@ -7195,12 +7195,12 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Bombon de gianduja de avellana</t>
+          <t>Bombón de gianduja de avellana</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="P73" s="13" t="inlineStr">
         <is>
-          <t>La gianduja tiene apartado propio en la norma (1.6.b.3), pero aqui va DENTRO de un bombon: la denominacion de venta que manda es la del producto que vendes, no la del relleno.</t>
+          <t>La gianduja tiene apartado propio en la norma (1.6.b.3), pero aquí va DENTRO de un bombón: la denominación de venta que manda es la del producto que vendes, no la del relleno.</t>
         </is>
       </c>
     </row>
@@ -7270,7 +7270,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="P74" s="13" t="inlineStr">
         <is>
-          <t>Aqui el 25 % se pelea: 4 g de chocolate sobre 13 g de pieza son el 30,8 %, y bajando el bano un gramo se cae por debajo del minimo legal. Es el ejemplo con el que el semaforo del libro 4 ensena para que sirve. «Trufa» no es una categoria legal espanola (`CHN-03b`).</t>
+          <t>Aquí el 25 % se pelea: 4 g de chocolate sobre 13 g de pieza son el 30,8 %, y bajando el baño un gramo se cae por debajo del mínimo legal. Es el ejemplo con el que el semáforo del libro 4 enseña para que sirve. «Trufa» no es una categoría legal española (`CHN-03b`).</t>
         </is>
       </c>
     </row>
@@ -7335,12 +7335,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Bombon de licor de ron</t>
+          <t>Bombón de licor de ron</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="P75" s="13" t="inlineStr">
         <is>
-          <t>Cascara mas gruesa (6 g) porque el licor la ataca. La unica del surtido sin leche: si la vendes a granel al lado de las demas, la contaminacion cruzada en la pinza se come esa ventaja.</t>
+          <t>Cascara mas gruesa (6 g) porque el licor la ataca. La única del surtido sin leche: si la vendes a granel al lado de las demás, la contaminación cruzada en la pinza se come esa ventaja.</t>
         </is>
       </c>
     </row>
@@ -7405,12 +7405,12 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Bombon de caramelo salado</t>
+          <t>Bombón de caramelo salado</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="P76" s="13" t="inlineStr">
         <is>
-          <t>Azucar alto y agua baja: aguanta mucho mas que una ganache fresca.</t>
+          <t>Azúcar alto y agua baja: aguanta mucho mas que una ganache fresca.</t>
         </is>
       </c>
     </row>
@@ -7475,12 +7475,12 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Bombon de praline de cacahuete</t>
+          <t>Bombón de praline de cacahuete</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -7545,12 +7545,12 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Bombon crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sesamo y barquillo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="P78" s="13" t="inlineStr">
         <is>
-          <t>Dos alergenos mas que sus companeras, y los dos independientes: granos de sesamo (punto 11) y cereales con gluten del barquillo (punto 1). El kit le da 3-4 semanas, y no por seguridad: pierde el crujiente mucho antes.</t>
+          <t>Dos alérgenos mas que sus companeras, y los dos independientes: granos de sesamo (punto 11) y cereales con gluten del barquillo (punto 1). El kit le da 3-4 semanas, y no por seguridad: pierde el crujiente mucho antes.</t>
         </is>
       </c>
     </row>
@@ -7615,12 +7615,12 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Bombon de naranja confitada y chocolate negro</t>
+          <t>Bombón de naranja confitada y chocolate negro</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="P79" s="13" t="inlineStr">
         <is>
-          <t>La unica del surtido con SULFITOS, que es el octavo alergeno y el que mas se olvida: la fruta confitada suele llevarlos y el umbral de declaracion es de 10 mg/kg. La fruta ademas contamina el recorte: su merma NO recuperable es la mas alta de la carta (D40).</t>
+          <t>La única del surtido con SULFITOS, que es el octavo alérgeno y el que mas se olvida: la fruta confitada suele llevarlos y el umbral de declaración es de 10 mg/kg. La fruta además contamina el recorte: su merma NO recuperable es la mas alta de la carta (D40).</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="P80" s="13" t="inlineStr">
         <is>
-          <t>La referencia que vende el posicionamiento: cobertura de origen a 37,48 euros/kg (`CHS-28c`) frente a los 25,02 de la de marca (`CHS-28a`), factor 1,5. Lleva la mencion «cacao: X % minimo» obligatoria (`CHN-07`) y es la que mas sube en verano: no lleva agua, aguanta 12-18 meses y viaja. Y es la referencia con el food cost MAS ALTO de la carta, con diferencia: comprar cobertura de origen y ponerle precio de cobertura de marca es como se regala el trabajo. El libro 3 lo ensena con el escenario de subida del cacao.</t>
+          <t>La referencia que vende el posicionamiento: cobertura de origen a 37,48 euros/kg (`CHS-28c`) frente a los 25,02 de la de marca (`CHS-28a`), factor 1,5. Lleva la mención «cacao: X % mínimo» obligatoria (`CHN-07`) y es la que mas sube en verano: no lleva agua, aguanta 12-18 meses y viaja. Y es la referencia con el food cost MAS ALTO de la carta, con diferencia: comprar cobertura de origen y ponerle precio de cobertura de marca es como se regala el trabajo. El libro 3 lo enseña con el escenario de subida del cacao.</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="P81" s="13" t="inlineStr">
         <is>
-          <t>Tambien lleva la mencion «cacao: X % minimo» (`CHN-07`).</t>
+          <t>También lleva la mención «cacao: X % mínimo» (`CHN-07`).</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="P82" s="13" t="inlineStr">
         <is>
-          <t>El chocolate blanco NO lleva la mencion «cacao: X % minimo»: `CHN-07` acota esa obligacion a los apartados 1.4, 1.5, 1.6, 1.7, 1.8, 1.11 y 1.12, y el blanco es el 1.9. Escribir que la mencion es obligatoria en todos los chocolates esta prohibido (§5.1, 27).</t>
+          <t>El chocolate blanco NO lleva la mención «cacao: X % mínimo»: `CHN-07` acota esa obligación a los apartados 1.4, 1.5, 1.6, 1.7, 1.8, 1.11 y 1.12, y el blanco es el 1.9. Escribir que la mención es obligatoria en todos los chocolates esta prohibido (§5.1, 27).</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="P83" s="13" t="inlineStr">
         <is>
-          <t>La almendra va en `g_relleno` porque es materia comestible ANADIDA del ap. 3, y su tope es el 40 % del peso total (`CHN-09`). Con 22 g sobre 100 esta en el 22 %: dentro. La almendra enrancia, y el frio no lo evita: manda la fecha, no el aspecto (nota del kit).</t>
+          <t>La almendra va en `g_relleno` porque es materia comestible AÑADIDA del ap. 3, y su tope es el 40 % del peso total (`CHN-09`). Con 22 g sobre 100 esta en el 22 %: dentro. La almendra enrancia, y el frío no lo evita: manda la fecha, no el aspecto (nota del kit).</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="P84" s="13" t="inlineStr">
         <is>
-          <t>La avellana va como materia anadida del ap. 3, igual que la almendra de TB4.</t>
+          <t>La avellana va como materia añadida del ap. 3, igual que la almendra de TB4.</t>
         </is>
       </c>
     </row>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="P85" s="13" t="inlineStr">
         <is>
-          <t>La segunda referencia del ap. 1.10, y la que ensena la base de calculo: 55 g de chocolate sobre 100 g de pieza son el 55 %, calculado SOBRE EL PESO TOTAL con el relleno dentro (`CHN-10`). Si alguien lo calculase descontando el relleno le saldria el 100 % y el semaforo dejaria pasar cualquier cosa: por eso invertir las dos bases esta prohibido. Y NO es chocolate relleno lo que lleva interior de panaderia, pasteleria, galleteria, bolleria o helado (`CHN-04`).</t>
+          <t>La segunda referencia del ap. 1.10, y la que enseña la base de calculo: 55 g de chocolate sobre 100 g de pieza son el 55 %, calculado SOBRE EL PESO TOTAL con el relleno dentro (`CHN-10`). Si alguien lo calculase descontando el relleno le saldria el 100 % y el semáforo dejaría pasar cualquier cosa: por eso invertir las dos bases esta prohibido. Y NO es chocolate relleno lo que lleva interior de panadería, pastelería, galleteria, bollería o helado (`CHN-04`).</t>
         </is>
       </c>
     </row>
@@ -8160,7 +8160,7 @@
       </c>
       <c r="P86" s="13" t="inlineStr">
         <is>
-          <t>El almidon (9,6 g sobre 200, el 4,8 %) esta por debajo del tope del 8 %. Se usa ALMIDON DE MAIZ a proposito: con almidon de TRIGO habria que declarar gluten, y la norma admite los tres. La etiqueta lleva ademas la expresion «para su consumo cocido» (ap. 6.e): es una ADICION ESPANOLA que NO existe en la Directiva 2000/36/CE (`CHN-83`), asi que no se escribe que sea un requisito europeo.</t>
+          <t>El almidón (9,6 g sobre 200, el 4,8 %) esta por debajo del tope del 8 %. Se usa ALMIDÓN DE MAÍZ a propósito: con almidón de TRIGO habría que declarar gluten, y la norma admite los tres. La etiqueta lleva además la expresión «para su consumo cocido» (ap. 6.e): es una ADICION ESPAÑOLA que NO existe en la Directiva 2000/36/CE (`CHN-83`), así que no se escribe que sea un requisito europeo.</t>
         </is>
       </c>
     </row>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="P87" s="13" t="inlineStr">
         <is>
-          <t>Seis sobres de 30 g. Ojo al art. 2.2.c) del RD 1808/1991: los envases cuya cara mayor mide menos de 10 cm2 estan exentos de lote, pero la CAJA que los contiene no (`CHN-36`).</t>
+          <t>Seis sobres de 30 g. Ojo al art. 2.2.c) del RD 1808/1991: los envases cuya cara mayor mide menos de 10 cm2 están exentos de lote, pero la CAJA que los contiene no (`CHN-36`).</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="P88" s="13" t="inlineStr">
         <is>
-          <t>Aqui NO entregas un bien: prestas un servicio de hosteleria, y el IVA va al 10 % por el art. 91.Uno.2.2.o (`CHN-71c`). No lleva etiqueta, asi que su referencia es tu sistema de autocontrol (D47). Y si pones mesas, el art. 8 de la Ley 1/2025 te obliga a facilitar que el cliente se lleve lo que no ha consumido, aunque seas microempresa: la exclusion del art. 6.6 NO alcanza al art. 8 (`CHN-92`). Es la pieza que sube el ticket del churro un 40-60 % en la variante de taza (`CHS-32`), y es OTRO negocio (D1).</t>
+          <t>Aquí NO entregas un bien: prestas un servicio de hostelería, y el IVA va al 10 % por el art. 91.Uno.2.2.o (`CHN-71c`). No lleva etiqueta, así que su referencia es tu sistema de autocontrol (D47). Y si pones mesas, el art. 8 de la Ley 1/2025 te obliga a facilitar que el cliente se lleve lo que no ha consumido, aunque seas microempresa: la exclusión del art. 6.6 NO alcanza al art. 8 (`CHN-92`). Es la pieza que sube el ticket del churro un 40-60 % en la variante de taza (`CHS-32`), y es OTRO negocio (D1).</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="P89" s="13" t="inlineStr">
         <is>
-          <t>La merma recuperable mas alta del catalogo: la pieza hueca se raja con los cambios bruscos de temperatura (nota del kit) y lo que se rompe SIN relleno vuelve entero a la cuba. Cero mix en verano: es de campana.</t>
+          <t>La merma recuperable mas alta del catálogo: la pieza hueca se raja con los cambios bruscos de temperatura (nota del kit) y lo que se rompe SIN relleno vuelve entero a la cuba. Cero mix en verano: es de campana.</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="P90" s="13" t="inlineStr">
         <is>
-          <t>Pieza de autor y la que mas minutos de obrador se lleva: 210 por tanda de seis. La decoracion va como materia anadida del ap. 3. Es la referencia que pone a prueba la capacidad del libro 1 en abril.</t>
+          <t>Pieza de autor y la que mas minutos de obrador se lleva: 210 por tanda de seis. La decoración va como materia añadida del ap. 3. Es la referencia que pone a prueba la capacidad del libro 1 en abril.</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="P91" s="13" t="inlineStr">
         <is>
-          <t>LA REFERENCIA QUE ROMPE LA REGLA, y por eso esta aqui: 9 g de chocolate sobre 30 g de pieza son el 30 %, pero NO es un bombon de chocolate, porque el 1.13 pide una pieza «del tamano de un bocado constituida por chocolate», y esto es un producto de confiteria RECUBIERTO. Su denominacion sale del RD 348/2011 (`CHN-15`), no del RD 1055/2003. La UNICA con huevo, por la yema, y va con ovoproducto pasteurizado (`CHN-31`). Esta literalmente en el calendario del kit: «Todos los Santos (1): panellets y huesos de santo banados».</t>
+          <t>LA REFERENCIA QUE ROMPE LA REGLA, y por eso esta aquí: 9 g de chocolate sobre 30 g de pieza son el 30 %, pero NO es un bombón de chocolate, porque el 1.13 pide una pieza «del tamaño de un bocado constituida por chocolate», y esto es un producto de confitería RECUBIERTO. Su denominación sale del RD 348/2011 (`CHN-15`), no del RD 1055/2003. La ÚNICA con huevo, por la yema, y va con ovoproducto pasteurizado (`CHN-31`). Esta literalmente en el calendario del kit: «Todos los Santos (1): panellets y huesos de santo banados».</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Turron de chocolate con almendra, 250 g</t>
+          <t>Turrón de chocolate con almendra, 250 g</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="P92" s="13" t="inlineStr">
         <is>
-          <t>HUECO DECLARADO: la denominacion que publica este juego de datos es la del RD 1055/2003, porque la norma de calidad de TURRONES no se abrio en la verificacion legal del 12-09-2026 y ninguna ficha `CHN-*` la cubre. «Turron de chocolate con almendra» es el NOMBRE COMERCIAL; antes de imprimir la etiqueta hay que comprobar si la norma de turrones te obliga a otra denominacion de venta. La almendra (82 g sobre 250, el 32,8 %) esta dentro del tope del 40 % del ap. 3 (`CHN-09`).</t>
+          <t>HUECO DECLARADO: la denominación que publica este juego de datos es la del RD 1055/2003, porque la norma de calidad de TURRONES no se abrio en la verificación legal del 12-09-2026 y ninguna ficha `CHN-*` la cubre. «Turrón de chocolate con almendra» es el NOMBRE COMERCIAL; antes de imprimir la etiqueta hay que comprobar si la norma de turrones te obliga a otra denominación de venta. La almendra (82 g sobre 250, el 32,8 %) esta dentro del tope del 40 % del ap. 3 (`CHN-09`).</t>
         </is>
       </c>
     </row>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="P93" s="13" t="inlineStr">
         <is>
-          <t>La que da nombre a la casa, y su denominacion NO sale del RD 1055/2003 sino del RD 348/2011: «grageas o confites de chocolate» (`CHN-15`). Se hace en bombo, no en molde: `moldes_tanda` vale 1 y los 95 minutos son de la tanda entera, de la que salen 40 bolsas. Es la segunda que mas sube en verano: no lleva agua y es souvenir (literal del kit para julio: «packs souvenir y colaboraciones locales»).</t>
+          <t>La que da nombre a la casa, y su denominación NO sale del RD 1055/2003 sino del RD 348/2011: «grageas o confites de chocolate» (`CHN-15`). Se hace en bombo, no en molde: `moldes_tanda` vale 1 y los 95 minutos son de la tanda entera, de la que salen 40 bolsas. Es la segunda que mas sube en verano: no lleva agua y es souvenir (literal del kit para julio: «packs souvenir y colaboraciones locales»).</t>
         </is>
       </c>
     </row>
@@ -8944,7 +8944,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>DOS tasas por referencia, y la regla es del kit: «El chocolate sin relleno y sin contaminar se puede refundir; el que lleva ganache o fruta, a residuo» (02-partidas-produccion.xlsx!Moldeado). Lo que vuelve a la cuba no encarece la materia; lo que se tira, sí.</t>
+          <t>DOS tasas por referencia, y la regla es del kit: «El chocolate sin relleno y sin contaminar se puede refundir; el que lleva ganache o fruta, a residuo» (02-partidas-produccion.xlsx, hoja «Moldeado»). Lo que vuelve a la cuba no encarece la materia; lo que se tira, sí.</t>
         </is>
       </c>
     </row>
@@ -9040,7 +9040,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Bombon de ganache de chocolate negro 70 %</t>
+          <t>Bombón de ganache de chocolate negro 70 %</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Bombon de ganache de leche y vainilla</t>
+          <t>Bombón de ganache de leche y vainilla</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Bombon de praline de avellana</t>
+          <t>Bombón de praline de avellana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Bombon de gianduja de avellana</t>
+          <t>Bombón de gianduja de avellana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Bombon de licor de ron</t>
+          <t>Bombón de licor de ron</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Bombon de caramelo salado</t>
+          <t>Bombón de caramelo salado</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Bombon de praline de cacahuete</t>
+          <t>Bombón de praline de cacahuete</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Bombon crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sesamo y barquillo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Bombon de naranja confitada y chocolate negro</t>
+          <t>Bombón de naranja confitada y chocolate negro</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Turron de chocolate con almendra, 250 g</t>
+          <t>Turrón de chocolate con almendra, 250 g</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Bombon de ganache de chocolate negro 70 %</t>
+          <t>Bombón de ganache de chocolate negro 70 %</t>
         </is>
       </c>
       <c r="C7" s="17" t="n">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Bombon de ganache de leche y vainilla</t>
+          <t>Bombón de ganache de leche y vainilla</t>
         </is>
       </c>
       <c r="C8" s="17" t="n">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Bombon de praline de avellana</t>
+          <t>Bombón de praline de avellana</t>
         </is>
       </c>
       <c r="C9" s="17" t="n">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Bombon de gianduja de avellana</t>
+          <t>Bombón de gianduja de avellana</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
@@ -11607,7 +11607,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Bombon de licor de ron</t>
+          <t>Bombón de licor de ron</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Bombon de caramelo salado</t>
+          <t>Bombón de caramelo salado</t>
         </is>
       </c>
       <c r="C13" s="17" t="n">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Bombon de praline de cacahuete</t>
+          <t>Bombón de praline de cacahuete</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Bombon crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sesamo y barquillo</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Bombon de naranja confitada y chocolate negro</t>
+          <t>Bombón de naranja confitada y chocolate negro</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
@@ -13103,7 +13103,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Turron de chocolate con almendra, 250 g</t>
+          <t>Turrón de chocolate con almendra, 250 g</t>
         </is>
       </c>
       <c r="C29" s="17" t="n">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Bombon de ganache de chocolate negro 70 %</t>
+          <t>Bombón de ganache de chocolate negro 70 %</t>
         </is>
       </c>
       <c r="C7" s="17" t="n">
@@ -13833,7 +13833,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Bombon de ganache de leche y vainilla</t>
+          <t>Bombón de ganache de leche y vainilla</t>
         </is>
       </c>
       <c r="C8" s="17" t="n">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Bombon de praline de avellana</t>
+          <t>Bombón de praline de avellana</t>
         </is>
       </c>
       <c r="C9" s="17" t="n">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Bombon de gianduja de avellana</t>
+          <t>Bombón de gianduja de avellana</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
@@ -13977,7 +13977,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Bombon de licor de ron</t>
+          <t>Bombón de licor de ron</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
@@ -14013,7 +14013,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Bombon de caramelo salado</t>
+          <t>Bombón de caramelo salado</t>
         </is>
       </c>
       <c r="C13" s="17" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Bombon de praline de cacahuete</t>
+          <t>Bombón de praline de cacahuete</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Bombon crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sesamo y barquillo</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Bombon de naranja confitada y chocolate negro</t>
+          <t>Bombón de naranja confitada y chocolate negro</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
@@ -14814,12 +14814,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Bombon de ganache de chocolate negro 70 %</t>
+          <t>Bombón de ganache de chocolate negro 70 %</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
@@ -14861,12 +14861,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Bombon de ganache de leche y vainilla</t>
+          <t>Bombón de ganache de leche y vainilla</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
@@ -14908,12 +14908,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Bombon de praline de avellana</t>
+          <t>Bombón de praline de avellana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
@@ -14955,12 +14955,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Bombon de gianduja de avellana</t>
+          <t>Bombón de gianduja de avellana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
@@ -15049,12 +15049,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Bombon de licor de ron</t>
+          <t>Bombón de licor de ron</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
@@ -15096,12 +15096,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Bombon de caramelo salado</t>
+          <t>Bombón de caramelo salado</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
@@ -15143,12 +15143,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Bombon de praline de cacahuete</t>
+          <t>Bombón de praline de cacahuete</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
@@ -15190,12 +15190,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Bombon crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sesamo y barquillo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
@@ -15237,12 +15237,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Bombon de naranja confitada y chocolate negro</t>
+          <t>Bombón de naranja confitada y chocolate negro</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
@@ -15848,7 +15848,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Turron de chocolate con almendra, 250 g</t>
+          <t>Turrón de chocolate con almendra, 250 g</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -16462,12 +16462,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Bombon de ganache de chocolate negro 70 %</t>
+          <t>Bombón de ganache de chocolate negro 70 %</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D7" s="28">
@@ -16516,12 +16516,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Bombon de ganache de leche y vainilla</t>
+          <t>Bombón de ganache de leche y vainilla</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D8" s="28">
@@ -16570,12 +16570,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Bombon de praline de avellana</t>
+          <t>Bombón de praline de avellana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D9" s="28">
@@ -16624,12 +16624,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Bombon de gianduja de avellana</t>
+          <t>Bombón de gianduja de avellana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D10" s="28">
@@ -16683,7 +16683,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D11" s="28">
@@ -16732,12 +16732,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Bombon de licor de ron</t>
+          <t>Bombón de licor de ron</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D12" s="28">
@@ -16786,12 +16786,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Bombon de caramelo salado</t>
+          <t>Bombón de caramelo salado</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D13" s="28">
@@ -16840,12 +16840,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Bombon de praline de cacahuete</t>
+          <t>Bombón de praline de cacahuete</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D14" s="28">
@@ -16894,12 +16894,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Bombon crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sesamo y barquillo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D15" s="28">
@@ -16948,12 +16948,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Bombon de naranja confitada y chocolate negro</t>
+          <t>Bombón de naranja confitada y chocolate negro</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bombones de coleccion</t>
+          <t>Bombones de colección</t>
         </is>
       </c>
       <c r="D16" s="28">
@@ -17650,7 +17650,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Turron de chocolate con almendra, 250 g</t>
+          <t>Turrón de chocolate con almendra, 250 g</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">

--- a/scripts/productos-digitales/guia-chocolateria/build/carta-de-apertura-y-escandallo-chocolate.xlsx
+++ b/scripts/productos-digitales/guia-chocolateria/build/carta-de-apertura-y-escandallo-chocolate.xlsx
@@ -2408,7 +2408,7 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Pasta de sesamo</t>
+          <t>Pasta de sésamo</t>
         </is>
       </c>
       <c r="B65" s="23" t="n">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Bombón de praline de avellana</t>
+          <t>Bombón de praliné de avellana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Bombón de chocolate (praline)</t>
+          <t>Bombón de chocolate (praliné)</t>
         </is>
       </c>
       <c r="E9" s="18" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Bombón de praline de cacahuete</t>
+          <t>Bombón de praliné de cacahuete</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Bombón de chocolate (praline)</t>
+          <t>Bombón de chocolate (praliné)</t>
         </is>
       </c>
       <c r="E14" s="18" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="O14" s="13" t="inlineStr">
         <is>
-          <t>LA REFERENCIA QUE DEMUESTRA POR QUE SON OCHO Y NO CINCO: el cacahuete es el punto 5 del Anexo II y NO es un fruto de cascara (punto 8). Meterlo dentro de «frutos secos» es un error de etiquetado que puede mandar a alguien al hospital.</t>
+          <t>LA REFERENCIA QUE DEMUESTRA POR QUE SON OCHO Y NO CINCO: el cacahuete es el punto 5 del Anexo II y NO es un fruto de cáscara (punto 8). Meterlo dentro de «frutos secos» es un error de etiquetado que puede mandar a alguien al hospital.</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Bombón crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sésamo y barquillo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="O15" s="13" t="inlineStr">
         <is>
-          <t>Dos alérgenos mas que sus companeras, y los dos independientes: granos de sesamo (punto 11) y cereales con gluten del barquillo (punto 1). El kit le da 3-4 semanas, y no por seguridad: pierde el crujiente mucho antes.</t>
+          <t>Dos alérgenos mas que sus compañeras, y los dos independientes: granos de sésamo (punto 11) y cereales con gluten del barquillo (punto 1). El kit le da 3-4 semanas, y no por seguridad: pierde el crujiente mucho antes.</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="F19" s="29" t="inlineStr">
         <is>
-          <t>ap. 1.9: 20 % de manteca, 14 % de materia seca lactea, 3,5 % de grasa lactea</t>
+          <t>ap. 1.9: 20 % de manteca, 14 % de materia seca láctea, 3,5 % de grasa láctea</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Tableta rellena de praline, 100 g</t>
+          <t>Tableta rellena de praliné, 100 g</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Hueso de santo banado en chocolate</t>
+          <t>Hueso de santo bañado en chocolate</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="F28" s="29" t="inlineStr">
         <is>
-          <t>RD 348/2011: si el producto esta relleno, recubierto o grageado, la denominación de venta tiene que decirlo</t>
+          <t>RD 348/2011: si el producto está relleno, recubierto o grageado, la denominación de venta tiene que decirlo</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="O28" s="13" t="inlineStr">
         <is>
-          <t>LA REFERENCIA QUE ROMPE LA REGLA, y por eso esta aquí: 9 g de chocolate sobre 30 g de pieza son el 30 %, pero NO es un bombón de chocolate, porque el 1.13 pide una pieza «del tamaño de un bocado constituida por chocolate», y esto es un producto de confitería RECUBIERTO. Su denominación sale del RD 348/2011 (`CHN-15`), no del RD 1055/2003. La ÚNICA con huevo, por la yema, y va con ovoproducto pasteurizado (`CHN-31`). Esta literalmente en el calendario del kit: «Todos los Santos (1): panellets y huesos de santo banados».</t>
+          <t>LA REFERENCIA QUE ROMPE LA REGLA, y por eso esta aquí: 9 g de chocolate sobre 30 g de pieza son el 30 %, pero NO es un bombón de chocolate, porque el 1.13 pide una pieza «del tamaño de un bocado constituida por chocolate», y esto es un producto de confitería RECUBIERTO. Su denominación sale del RD 348/2011 (`CHN-15`), no del RD 1055/2003. La ÚNICA con huevo, por la yema, y va con ovoproducto pasteurizado (`CHN-31`). Esta literalmente en el calendario del kit: «Todos los Santos (1): panellets y huesos de santo bañados».</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Almendras marcona banadas en chocolate, bolsa de 150 g</t>
+          <t>Almendras marcona bañadas en chocolate, bolsa de 150 g</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="F31" s="29" t="inlineStr">
         <is>
-          <t>ap. 6.a) y 6.c): la denominación va por pieza o, si el surtido es de los aps. 1.6 a 1.10 y 1.13, se sustituye por la de surtido, con una única lista de ingredientes. Es una DECISION de etiquetado, no una obligación</t>
+          <t>ap. 6.a) y 6.c): la denominación va por pieza o, si el surtido es de los aps. 1.6 a 1.10 y 1.13, se sustituye por la de surtido, con una única lista de ingredientes. Es una DECISIÓN de etiquetado, no una obligación</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4810,7 +4810,7 @@
     <row r="35" ht="46" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>ENVASADO CON ETIQUETA: Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (`CHN-35`) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (`CHN-36`).</t>
+          <t>ENVASADO CON ETIQUETA: Sale envasado con SU etiqueta. El art. 4.2 del RD 1021/2022 fija la temperatura de conservación POR LA ETIQUETA que pone quien ha producido y envasado: la que tu has escrito te obliga a ti. Y con etiqueta entran además las doce menciones del art. 9.1 del Rgto. 1169/2011 (CHN-35) mas el lote, que NO viene de ese reglamento sino del RD 1808/1991 (CHN-36).</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>praline avellana</t>
+          <t>praliné avellana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5541,7 +5541,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>praline avellana</t>
+          <t>praliné avellana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5569,7 +5569,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>praline avellana</t>
+          <t>praliné avellana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6017,7 +6017,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>praline cacahuete</t>
+          <t>praliné cacahuete</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>praline cacahuete</t>
+          <t>praliné cacahuete</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6073,7 +6073,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>praline cacahuete</t>
+          <t>praliné cacahuete</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6101,12 +6101,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>crujiente sesamo</t>
+          <t>crujiente sésamo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pasta de sesamo</t>
+          <t>Pasta de sésamo</t>
         </is>
       </c>
       <c r="C36" s="31" t="n">
@@ -6129,7 +6129,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>crujiente sesamo</t>
+          <t>crujiente sésamo</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6157,7 +6157,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>crujiente sesamo</t>
+          <t>crujiente sésamo</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6241,7 +6241,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>praline de tableta</t>
+          <t>praliné de tableta</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6269,7 +6269,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>praline de tableta</t>
+          <t>praliné de tableta</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6552,7 +6552,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>praline avellana</t>
+          <t>praliné avellana</t>
         </is>
       </c>
       <c r="B54" s="28">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Bombones de praline, gianduja y frutos secos</t>
+          <t>Bombones de praliné, gianduja y frutos secos</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>«Praline» NO es un nombre comercial: el punto 10 de la parte A del Anexo I de la Directiva 2000/36/CE se titula «Bombón de chocolate o praline» (`CHN-82`), con el mismo mínimo del 25 %.</t>
+          <t>«Praline» NO es un nombre comercial: el punto 10 de la parte A del Anexo I de la Directiva 2000/36/CE se titula «Bombón de chocolate o praliné» (`CHN-82`), con el mismo mínimo del 25 %.</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Bombones de praline, gianduja y frutos secos</t>
+          <t>Bombones de praliné, gianduja y frutos secos</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>El alcohol baja la actividad de agua. Vigilar la cristalización del azúcar en la cascara: revienta y gotea (nota literal del kit).</t>
+          <t>El alcohol baja la actividad de agua. Vigilar la cristalización del azúcar en la cáscara: revienta y gotea (nota literal del kit).</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>praline cacahuete</t>
+          <t>praliné cacahuete</t>
         </is>
       </c>
       <c r="B59" s="28">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Bombones de praline, gianduja y frutos secos</t>
+          <t>Bombones de praliné, gianduja y frutos secos</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6701,14 +6701,14 @@
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>EL CACAHUETE ES EL PUNTO 5 DEL ANEXO II y NO es un fruto de cascara (`CHN-34b`): esta referencia se etiqueta con su propio alérgeno, no dentro de «frutos secos».</t>
+          <t>EL CACAHUETE ES EL PUNTO 5 DEL ANEXO II y NO es un fruto de cáscara (`CHN-34b`): esta referencia se etiqueta con su propio alérgeno, no dentro de «frutos secos».</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>crujiente sesamo</t>
+          <t>crujiente sésamo</t>
         </is>
       </c>
       <c r="B60" s="28">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Barquillos y crujientes banados</t>
+          <t>Barquillos y crujientes bañados</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>DOS alérgenos independientes en una sola pieza: granos de sesamo (punto 11) y cereales con gluten del barquillo (punto 1). El kit le da 3-4 semanas, y no por seguridad: pierde el crujiente mucho antes.</t>
+          <t>DOS alérgenos independientes en una sola pieza: granos de sésamo (punto 11) y cereales con gluten del barquillo (punto 1). El kit le da 3-4 semanas, y no por seguridad: pierde el crujiente mucho antes.</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Frutos secos garrapinados y frutas confitadas banadas</t>
+          <t>Frutos secos garrapiñados y frutas confitadas bañadas</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6760,7 +6760,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>praline de tableta</t>
+          <t>praliné de tableta</t>
         </is>
       </c>
       <c r="B62" s="28">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Bombones de praline, gianduja y frutos secos</t>
+          <t>Bombones de praliné, gianduja y frutos secos</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Bombón de praline de avellana</t>
+          <t>Bombón de praliné de avellana</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>praline avellana</t>
+          <t>praliné avellana</t>
         </is>
       </c>
       <c r="I72" s="28">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Bombón de praline de cacahuete</t>
+          <t>Bombón de praliné de cacahuete</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>praline cacahuete</t>
+          <t>praliné cacahuete</t>
         </is>
       </c>
       <c r="I77" s="28">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="P77" s="13" t="inlineStr">
         <is>
-          <t>LA REFERENCIA QUE DEMUESTRA POR QUE SON OCHO Y NO CINCO: el cacahuete es el punto 5 del Anexo II y NO es un fruto de cascara (punto 8). Meterlo dentro de «frutos secos» es un error de etiquetado que puede mandar a alguien al hospital.</t>
+          <t>LA REFERENCIA QUE DEMUESTRA POR QUE SON OCHO Y NO CINCO: el cacahuete es el punto 5 del Anexo II y NO es un fruto de cáscara (punto 8). Meterlo dentro de «frutos secos» es un error de etiquetado que puede mandar a alguien al hospital.</t>
         </is>
       </c>
     </row>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Bombón crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sésamo y barquillo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>crujiente sesamo</t>
+          <t>crujiente sésamo</t>
         </is>
       </c>
       <c r="I78" s="28">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="P78" s="13" t="inlineStr">
         <is>
-          <t>Dos alérgenos mas que sus companeras, y los dos independientes: granos de sesamo (punto 11) y cereales con gluten del barquillo (punto 1). El kit le da 3-4 semanas, y no por seguridad: pierde el crujiente mucho antes.</t>
+          <t>Dos alérgenos mas que sus compañeras, y los dos independientes: granos de sésamo (punto 11) y cereales con gluten del barquillo (punto 1). El kit le da 3-4 semanas, y no por seguridad: pierde el crujiente mucho antes.</t>
         </is>
       </c>
     </row>
@@ -8032,7 +8032,7 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Tableta rellena de praline, 100 g</t>
+          <t>Tableta rellena de praliné, 100 g</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>praline de tableta</t>
+          <t>praliné de tableta</t>
         </is>
       </c>
       <c r="I85" s="28">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Hueso de santo banado en chocolate</t>
+          <t>Hueso de santo bañado en chocolate</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="P91" s="13" t="inlineStr">
         <is>
-          <t>LA REFERENCIA QUE ROMPE LA REGLA, y por eso esta aquí: 9 g de chocolate sobre 30 g de pieza son el 30 %, pero NO es un bombón de chocolate, porque el 1.13 pide una pieza «del tamaño de un bocado constituida por chocolate», y esto es un producto de confitería RECUBIERTO. Su denominación sale del RD 348/2011 (`CHN-15`), no del RD 1055/2003. La ÚNICA con huevo, por la yema, y va con ovoproducto pasteurizado (`CHN-31`). Esta literalmente en el calendario del kit: «Todos los Santos (1): panellets y huesos de santo banados».</t>
+          <t>LA REFERENCIA QUE ROMPE LA REGLA, y por eso esta aquí: 9 g de chocolate sobre 30 g de pieza son el 30 %, pero NO es un bombón de chocolate, porque el 1.13 pide una pieza «del tamaño de un bocado constituida por chocolate», y esto es un producto de confitería RECUBIERTO. Su denominación sale del RD 348/2011 (`CHN-15`), no del RD 1055/2003. La ÚNICA con huevo, por la yema, y va con ovoproducto pasteurizado (`CHN-31`). Esta literalmente en el calendario del kit: «Todos los Santos (1): panellets y huesos de santo bañados».</t>
         </is>
       </c>
     </row>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Almendras marcona banadas en chocolate, bolsa de 150 g</t>
+          <t>Almendras marcona bañadas en chocolate, bolsa de 150 g</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Bombón de praline de avellana</t>
+          <t>Bombón de praliné de avellana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Bombón de praline de cacahuete</t>
+          <t>Bombón de praliné de cacahuete</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Bombón crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sésamo y barquillo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Tableta rellena de praline, 100 g</t>
+          <t>Tableta rellena de praliné, 100 g</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Hueso de santo banado en chocolate</t>
+          <t>Hueso de santo bañado en chocolate</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Almendras marcona banadas en chocolate, bolsa de 150 g</t>
+          <t>Almendras marcona bañadas en chocolate, bolsa de 150 g</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Bombón de praline de avellana</t>
+          <t>Bombón de praliné de avellana</t>
         </is>
       </c>
       <c r="C9" s="17" t="n">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Bombón de praline de cacahuete</t>
+          <t>Bombón de praliné de cacahuete</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Bombón crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sésamo y barquillo</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Tableta rellena de praline, 100 g</t>
+          <t>Tableta rellena de praliné, 100 g</t>
         </is>
       </c>
       <c r="C22" s="17" t="n">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Hueso de santo banado en chocolate</t>
+          <t>Hueso de santo bañado en chocolate</t>
         </is>
       </c>
       <c r="C28" s="17" t="n">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Almendras marcona banadas en chocolate, bolsa de 150 g</t>
+          <t>Almendras marcona bañadas en chocolate, bolsa de 150 g</t>
         </is>
       </c>
       <c r="C30" s="17" t="n">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Bombón de praline de avellana</t>
+          <t>Bombón de praliné de avellana</t>
         </is>
       </c>
       <c r="C9" s="17" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Bombón de praline de cacahuete</t>
+          <t>Bombón de praliné de cacahuete</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Bombón crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sésamo y barquillo</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
@@ -14908,7 +14908,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Bombón de praline de avellana</t>
+          <t>Bombón de praliné de avellana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Bombón de praline de cacahuete</t>
+          <t>Bombón de praliné de cacahuete</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -15190,7 +15190,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Bombón crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sésamo y barquillo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -15519,7 +15519,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Tableta rellena de praline, 100 g</t>
+          <t>Tableta rellena de praliné, 100 g</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -15801,7 +15801,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Hueso de santo banado en chocolate</t>
+          <t>Hueso de santo bañado en chocolate</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -15895,7 +15895,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Almendras marcona banadas en chocolate, bolsa de 150 g</t>
+          <t>Almendras marcona bañadas en chocolate, bolsa de 150 g</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -16570,7 +16570,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Bombón de praline de avellana</t>
+          <t>Bombón de praliné de avellana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Bombón de praline de cacahuete</t>
+          <t>Bombón de praliné de cacahuete</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -16894,7 +16894,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Bombón crujiente de sesamo y barquillo</t>
+          <t>Bombón crujiente de sésamo y barquillo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -17272,7 +17272,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Tableta rellena de praline, 100 g</t>
+          <t>Tableta rellena de praliné, 100 g</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -17596,7 +17596,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Hueso de santo banado en chocolate</t>
+          <t>Hueso de santo bañado en chocolate</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -17704,7 +17704,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Almendras marcona banadas en chocolate, bolsa de 150 g</t>
+          <t>Almendras marcona bañadas en chocolate, bolsa de 150 g</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
